--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,225 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="I13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -503,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0">
+    <comment ref="L16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -522,94 +740,6 @@
           </rPr>
           <t xml:space="preserve">
 对应配置表DailyRewards的ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-获得道具数量_购买原价_实际购买价格</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-渠道ID_商品ID|……</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-期数</t>
         </r>
       </text>
     </comment>
@@ -631,6 +761,72 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+获得道具数量_购买原价_实际购买价格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+渠道ID_商品ID|……</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 期数</t>
         </r>
       </text>
@@ -653,11 +849,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
+期数</t>
         </r>
       </text>
     </comment>
-    <comment ref="N24" authorId="0">
+    <comment ref="L27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -679,7 +897,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O24" authorId="0">
+    <comment ref="O27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -706,7 +924,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>序列ID</t>
   </si>
@@ -904,6 +1122,30 @@
   </si>
   <si>
     <t>180000000_10_3_2</t>
+  </si>
+  <si>
+    <t>59 59 23 9 * ?</t>
+  </si>
+  <si>
+    <t>60000000_10_1_2</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-17号开</t>
+  </si>
+  <si>
+    <t>0 0 0 17 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 19 * ?</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-27号开</t>
+  </si>
+  <si>
+    <t>0 0 0 27 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 29 * ?</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -1859,12 +2101,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2256,7 +2498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2643,17 +2885,17 @@
       <c r="J10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="9" t="b">
-        <v>1</v>
+      <c r="K10" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="31" t="s">
+      <c r="M10" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="31"/>
-      <c r="O10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="30"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
@@ -2684,17 +2926,17 @@
       <c r="J11" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="9" t="b">
-        <v>1</v>
+      <c r="K11" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="31" t="s">
+      <c r="M11" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="31"/>
-      <c r="O11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
       <c r="P11" s="30"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
@@ -2725,263 +2967,274 @@
       <c r="J12" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="9" t="b">
-        <v>1</v>
+      <c r="K12" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="31"/>
-      <c r="O12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="30"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
-        <v>57010</v>
+        <v>57104</v>
       </c>
       <c r="B13" s="9">
-        <v>57010</v>
+        <v>57009</v>
       </c>
       <c r="C13" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
-        <v>1</v>
-      </c>
-      <c r="H13" s="9">
-        <v>9999</v>
-      </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13" s="26"/>
+        <v>54</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>67</v>
+      </c>
       <c r="N13" s="26"/>
       <c r="O13" s="29"/>
       <c r="P13" s="30"/>
     </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="1">
-        <v>57011</v>
-      </c>
-      <c r="B14" s="1">
-        <v>57011</v>
-      </c>
-      <c r="C14" s="1">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
+    <row r="14" s="9" customFormat="1" spans="1:16">
+      <c r="A14" s="9">
+        <v>57105</v>
+      </c>
+      <c r="B14" s="9">
+        <v>57009</v>
+      </c>
+      <c r="C14" s="9">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G14" s="9">
+        <v>3</v>
+      </c>
+      <c r="I14" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9999</v>
+      <c r="J14" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="K14" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+    </row>
+    <row r="15" s="9" customFormat="1" spans="1:16">
+      <c r="A15" s="9">
+        <v>57106</v>
+      </c>
+      <c r="B15" s="9">
+        <v>57009</v>
+      </c>
+      <c r="C15" s="9">
+        <v>9</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="27"/>
-    </row>
-    <row r="15" s="10" customFormat="1" spans="1:16">
-      <c r="A15" s="10">
+      <c r="L15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="26"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
+    </row>
+    <row r="16" s="9" customFormat="1" spans="1:16">
+      <c r="A16" s="9">
+        <v>57010</v>
+      </c>
+      <c r="B16" s="9">
+        <v>57010</v>
+      </c>
+      <c r="C16" s="9">
+        <v>10</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1">
+        <v>57011</v>
+      </c>
+      <c r="B17" s="1">
+        <v>57011</v>
+      </c>
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="K17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="27"/>
+    </row>
+    <row r="18" s="10" customFormat="1" spans="1:18">
+      <c r="A18" s="10">
         <v>57012</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B18" s="10">
         <v>57012</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C18" s="10">
         <v>12</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G18" s="10">
         <v>1</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H18" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="34" t="b">
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="37"/>
-    </row>
-    <row r="16" s="10" customFormat="1" spans="1:16">
-      <c r="A16" s="10">
-        <v>57013</v>
-      </c>
-      <c r="B16" s="10">
-        <v>57013</v>
-      </c>
-      <c r="C16" s="10">
-        <v>13</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="37">
-        <v>46101</v>
-      </c>
-      <c r="G16" s="10">
-        <v>2</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="K16" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="37"/>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:18">
-      <c r="A17" s="10">
-        <v>57014</v>
-      </c>
-      <c r="B17" s="10">
-        <v>57014</v>
-      </c>
-      <c r="C17" s="10">
-        <v>14</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="37">
-        <v>46102</v>
-      </c>
-      <c r="G17" s="10">
-        <v>2</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:18">
-      <c r="A18" s="11">
-        <v>57015</v>
-      </c>
-      <c r="B18" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C18" s="11">
-        <v>15</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="11">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="N18" s="39" t="s">
+      <c r="L18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="O18" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="P18" s="40"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="37"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
-        <v>57016</v>
+        <v>57013</v>
       </c>
       <c r="B19" s="10">
-        <v>57016</v>
+        <v>57013</v>
       </c>
       <c r="C19" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="37">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="G19" s="10">
-        <v>1</v>
-      </c>
-      <c r="H19" s="10">
-        <v>90</v>
-      </c>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="34" t="b">
+        <v>2</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="31" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="35"/>
@@ -2989,273 +3242,394 @@
       <c r="O19" s="36"/>
       <c r="P19" s="37"/>
     </row>
-    <row r="20" s="12" customFormat="1" spans="1:18">
-      <c r="A20" s="12">
+    <row r="20" s="10" customFormat="1" spans="1:18">
+      <c r="A20" s="10">
+        <v>57014</v>
+      </c>
+      <c r="B20" s="10">
+        <v>57014</v>
+      </c>
+      <c r="C20" s="10">
+        <v>14</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="37">
+        <v>46102</v>
+      </c>
+      <c r="G20" s="10">
+        <v>2</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="37"/>
+    </row>
+    <row r="21" s="11" customFormat="1" spans="1:18">
+      <c r="A21" s="11">
+        <v>57015</v>
+      </c>
+      <c r="B21" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C21" s="11">
+        <v>15</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="N21" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="40"/>
+    </row>
+    <row r="22" s="10" customFormat="1" spans="1:18">
+      <c r="A22" s="10">
+        <v>57016</v>
+      </c>
+      <c r="B22" s="10">
+        <v>57016</v>
+      </c>
+      <c r="C22" s="10">
+        <v>16</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="37">
+        <v>46103</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10">
+        <v>90</v>
+      </c>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="37"/>
+    </row>
+    <row r="23" s="12" customFormat="1" spans="1:18">
+      <c r="A23" s="12">
         <v>57017</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B23" s="12">
         <v>57017</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C23" s="12">
         <v>17</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="12" t="s">
+      <c r="D23" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="12">
+      <c r="F23" s="41"/>
+      <c r="G23" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="42" t="s">
+      <c r="I23" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="34" t="b">
+      <c r="K23" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L23" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="41"/>
-    </row>
-    <row r="21" s="13" customFormat="1" spans="1:18">
-      <c r="A21" s="12">
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="41"/>
+    </row>
+    <row r="24" s="13" customFormat="1" spans="1:18">
+      <c r="A24" s="12">
         <v>57018</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B24" s="12">
         <v>57018</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C24" s="12">
         <v>18</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="12" t="s">
+      <c r="D24" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="12">
+      <c r="F24" s="41"/>
+      <c r="G24" s="12">
         <v>3</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J21" s="42" t="s">
+      <c r="H24" s="12"/>
+      <c r="I24" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="34" t="b">
+      <c r="K24" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L24" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-    </row>
-    <row r="22" s="14" customFormat="1" spans="1:18">
-      <c r="A22" s="12">
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+    </row>
+    <row r="25" s="14" customFormat="1" spans="1:18">
+      <c r="A25" s="12">
         <v>57019</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B25" s="14">
         <v>57019</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C25" s="12">
         <v>19</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="12" t="s">
+      <c r="D25" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F25" s="45">
         <v>46106</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G25" s="14">
         <v>2</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12">
-        <v>1</v>
-      </c>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="P22" s="47"/>
-    </row>
-    <row r="23" s="9" customFormat="1" spans="1:18">
-      <c r="A23" s="48">
-        <v>57020</v>
-      </c>
-      <c r="B23" s="9">
-        <v>57020</v>
-      </c>
-      <c r="C23" s="48">
-        <v>20</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="49">
-        <v>46106</v>
-      </c>
-      <c r="G23" s="9">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9">
-        <v>9999</v>
-      </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="48">
-        <v>1</v>
-      </c>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="P23" s="30"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:18">
-      <c r="A24" s="11">
-        <v>57021</v>
-      </c>
-      <c r="B24" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C24" s="11">
-        <v>15</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="11">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="M24" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="O24" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="P24" s="40"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:18">
-      <c r="A25" s="48">
-        <v>57022</v>
-      </c>
-      <c r="B25" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C25" s="1">
-        <v>21</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="H25" s="1"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J25" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="9" t="b">
+      <c r="K25" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12">
         <v>1</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="P25" s="47"/>
+    </row>
+    <row r="26" s="9" customFormat="1" spans="1:18">
+      <c r="A26" s="48">
+        <v>57020</v>
+      </c>
+      <c r="B26" s="9">
+        <v>57020</v>
+      </c>
+      <c r="C26" s="48">
+        <v>20</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="49">
+        <v>46106</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="48">
+        <v>1</v>
+      </c>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="P26" s="30"/>
+    </row>
+    <row r="27" s="11" customFormat="1" spans="1:18">
+      <c r="A27" s="11">
+        <v>57021</v>
+      </c>
+      <c r="B27" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C27" s="11">
+        <v>15</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="11">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M27" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="N27" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="40"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:18">
+      <c r="A28" s="48">
+        <v>57022</v>
+      </c>
+      <c r="B28" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F25">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F26">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3274,10 +3648,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3285,7 +3659,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3293,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3301,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3309,7 +3683,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3317,7 +3691,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3325,7 +3699,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3333,7 +3707,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3341,7 +3715,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3349,7 +3723,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3357,7 +3731,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3365,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3373,7 +3747,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3381,7 +3755,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3389,7 +3763,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3397,7 +3771,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3405,7 +3779,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3413,7 +3787,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3421,7 +3795,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0">
+    <comment ref="E13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -499,11 +499,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？</t>
+绑定手机后才可以参加活动</t>
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0">
+    <comment ref="L13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -521,12 +521,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？
-</t>
+对应配置表DailyRewards的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="M13" authorId="0">
+    <comment ref="L18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -544,17 +543,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-官方派奖：奖池金币数量
-总量 ÷ 平均中奖金额 = 中奖次数
-1000000000 ÷ 718000 = 1392.7577
-========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
-统计类型：充值 
-</t>
+配置表-GrowthFund.xlsx中的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0">
+    <comment ref="N18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -572,11 +565,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？</t>
+获得道具数量_购买原价_实际购买价格</t>
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0">
+    <comment ref="O18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -594,12 +587,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？
-</t>
+渠道ID_商品ID|……</t>
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0">
+    <comment ref="L20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -617,129 +609,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-官方派奖：奖池金币数量
-总量 ÷ 平均中奖金额 = 中奖次数
-1000000000 ÷ 718000 = 1392.7577
-========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
-统计类型：充值 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-秒 分 时 日期1,日期2,日期3 * ？
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-官方派奖：奖池金币数量
-总量 ÷ 平均中奖金额 = 中奖次数
-1000000000 ÷ 718000 = 1392.7577
-========================================
-参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
-统计类型：充值 
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-绑定手机后才可以参加活动</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-对应配置表DailyRewards的ID</t>
+期数</t>
         </r>
       </text>
     </comment>
@@ -761,72 +631,6 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-获得道具数量_购买原价_实际购买价格</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-渠道ID_商品ID|……</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L23" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
 期数</t>
         </r>
       </text>
@@ -849,11 +653,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-期数</t>
+配置表-GrowthFund.xlsx中的ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="L27" authorId="0">
+    <comment ref="N24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -871,33 +675,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
+获得道具数量_购买原价_实际购买价格</t>
         </r>
       </text>
     </comment>
-    <comment ref="N27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-获得道具数量_购买原价_实际购买价格</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O27" authorId="0">
+    <comment ref="O24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -924,7 +706,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
   <si>
     <t>序列ID</t>
   </si>
@@ -1122,30 +904,6 @@
   </si>
   <si>
     <t>180000000_10_3_2</t>
-  </si>
-  <si>
-    <t>59 59 23 9 * ?</t>
-  </si>
-  <si>
-    <t>60000000_10_1_2</t>
-  </si>
-  <si>
-    <t>付费-官方派奖(常驻)-17号开</t>
-  </si>
-  <si>
-    <t>0 0 0 17 * ?</t>
-  </si>
-  <si>
-    <t>59 59 23 19 * ?</t>
-  </si>
-  <si>
-    <t>付费-官方派奖(常驻)-27号开</t>
-  </si>
-  <si>
-    <t>0 0 0 27 * ?</t>
-  </si>
-  <si>
-    <t>59 59 23 29 * ?</t>
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
@@ -2101,12 +1859,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2498,7 +2256,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2885,17 +2643,17 @@
       <c r="J10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="31" t="b">
-        <v>0</v>
+      <c r="K10" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="30"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
@@ -2926,17 +2684,17 @@
       <c r="J11" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="31" t="b">
-        <v>0</v>
+      <c r="K11" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="M11" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="32"/>
-      <c r="O11" s="33"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="32"/>
       <c r="P11" s="30"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
@@ -2967,274 +2725,263 @@
       <c r="J12" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="31" t="b">
-        <v>0</v>
+      <c r="K12" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="M12" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="32"/>
-      <c r="O12" s="33"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32"/>
       <c r="P12" s="30"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
-        <v>57104</v>
+        <v>57010</v>
       </c>
       <c r="B13" s="9">
-        <v>57009</v>
+        <v>57010</v>
       </c>
       <c r="C13" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="30">
-        <v>46105</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F13" s="9"/>
       <c r="G13" s="9">
-        <v>3</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="32" t="s">
-        <v>67</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="M13" s="26"/>
       <c r="N13" s="26"/>
       <c r="O13" s="29"/>
       <c r="P13" s="30"/>
     </row>
-    <row r="14" s="9" customFormat="1" spans="1:16">
-      <c r="A14" s="9">
-        <v>57105</v>
-      </c>
-      <c r="B14" s="9">
-        <v>57009</v>
-      </c>
-      <c r="C14" s="9">
-        <v>9</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="9" t="s">
+    <row r="14" spans="1:16">
+      <c r="A14" s="1">
+        <v>57011</v>
+      </c>
+      <c r="B14" s="1">
+        <v>57011</v>
+      </c>
+      <c r="C14" s="1">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="30">
-        <v>46105</v>
-      </c>
-      <c r="G14" s="9">
-        <v>3</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>70</v>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9999</v>
       </c>
       <c r="K14" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L14" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>60</v>
-      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="26"/>
       <c r="N14" s="26"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="30"/>
-    </row>
-    <row r="15" s="9" customFormat="1" spans="1:16">
-      <c r="A15" s="9">
-        <v>57106</v>
-      </c>
-      <c r="B15" s="9">
-        <v>57009</v>
-      </c>
-      <c r="C15" s="9">
-        <v>9</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="O14" s="27"/>
+    </row>
+    <row r="15" s="10" customFormat="1" spans="1:16">
+      <c r="A15" s="10">
+        <v>57012</v>
+      </c>
+      <c r="B15" s="10">
+        <v>57012</v>
+      </c>
+      <c r="C15" s="10">
+        <v>12</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10">
+        <v>9999</v>
+      </c>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="37"/>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="1:16">
+      <c r="A16" s="10">
+        <v>57013</v>
+      </c>
+      <c r="B16" s="10">
+        <v>57013</v>
+      </c>
+      <c r="C16" s="10">
+        <v>13</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="30">
-        <v>46105</v>
-      </c>
-      <c r="G15" s="9">
-        <v>3</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="28" t="s">
+      <c r="F16" s="37">
+        <v>46101</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2</v>
+      </c>
+      <c r="I16" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="9" t="b">
+      <c r="J16" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="K16" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="37"/>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:18">
+      <c r="A17" s="10">
+        <v>57014</v>
+      </c>
+      <c r="B17" s="10">
+        <v>57014</v>
+      </c>
+      <c r="C17" s="10">
+        <v>14</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="37">
+        <v>46102</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="37"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:18">
+      <c r="A18" s="11">
+        <v>57015</v>
+      </c>
+      <c r="B18" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C18" s="11">
+        <v>15</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="11">
         <v>1</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M15" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="30"/>
-    </row>
-    <row r="16" s="9" customFormat="1" spans="1:16">
-      <c r="A16" s="9">
-        <v>57010</v>
-      </c>
-      <c r="B16" s="9">
-        <v>57010</v>
-      </c>
-      <c r="C16" s="9">
-        <v>10</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="H18" s="1">
         <v>9999</v>
       </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="30"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1">
-        <v>57011</v>
-      </c>
-      <c r="B17" s="1">
-        <v>57011</v>
-      </c>
-      <c r="C17" s="1">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
-        <v>9999</v>
-      </c>
-      <c r="K17" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" s="1">
-        <v>1</v>
-      </c>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="27"/>
-    </row>
-    <row r="18" s="10" customFormat="1" spans="1:18">
-      <c r="A18" s="10">
-        <v>57012</v>
-      </c>
-      <c r="B18" s="10">
-        <v>57012</v>
-      </c>
-      <c r="C18" s="10">
-        <v>12</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="M18" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="10">
-        <v>1</v>
-      </c>
-      <c r="H18" s="10">
-        <v>9999</v>
-      </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="10" t="s">
+      <c r="N18" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="37"/>
+      <c r="O18" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="P18" s="40"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
-        <v>57013</v>
+        <v>57016</v>
       </c>
       <c r="B19" s="10">
-        <v>57013</v>
+        <v>57016</v>
       </c>
       <c r="C19" s="10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="37">
-        <v>46101</v>
+        <v>46103</v>
       </c>
       <c r="G19" s="10">
-        <v>2</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="J19" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="K19" s="31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="10">
+        <v>90</v>
+      </c>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="35"/>
@@ -3242,394 +2989,273 @@
       <c r="O19" s="36"/>
       <c r="P19" s="37"/>
     </row>
-    <row r="20" s="10" customFormat="1" spans="1:18">
-      <c r="A20" s="10">
-        <v>57014</v>
-      </c>
-      <c r="B20" s="10">
-        <v>57014</v>
-      </c>
-      <c r="C20" s="10">
-        <v>14</v>
-      </c>
-      <c r="D20" s="10" t="s">
+    <row r="20" s="12" customFormat="1" spans="1:18">
+      <c r="A20" s="12">
+        <v>57017</v>
+      </c>
+      <c r="B20" s="12">
+        <v>57017</v>
+      </c>
+      <c r="C20" s="12">
+        <v>17</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="41"/>
+      <c r="G20" s="12">
+        <v>3</v>
+      </c>
+      <c r="I20" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="J20" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K20" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="41"/>
+    </row>
+    <row r="21" s="13" customFormat="1" spans="1:18">
+      <c r="A21" s="12">
+        <v>57018</v>
+      </c>
+      <c r="B21" s="12">
+        <v>57018</v>
+      </c>
+      <c r="C21" s="12">
+        <v>18</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="37">
-        <v>46102</v>
-      </c>
-      <c r="G20" s="10">
+      <c r="F21" s="41"/>
+      <c r="G21" s="12">
+        <v>3</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+    </row>
+    <row r="22" s="14" customFormat="1" spans="1:18">
+      <c r="A22" s="12">
+        <v>57019</v>
+      </c>
+      <c r="B22" s="14">
+        <v>57019</v>
+      </c>
+      <c r="C22" s="12">
+        <v>19</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="45">
+        <v>46106</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="K20" s="31" t="b">
+      <c r="H22" s="14"/>
+      <c r="I22" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="37"/>
-    </row>
-    <row r="21" s="11" customFormat="1" spans="1:18">
-      <c r="A21" s="11">
+      <c r="L22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="P22" s="47"/>
+    </row>
+    <row r="23" s="9" customFormat="1" spans="1:18">
+      <c r="A23" s="48">
+        <v>57020</v>
+      </c>
+      <c r="B23" s="9">
+        <v>57020</v>
+      </c>
+      <c r="C23" s="48">
+        <v>20</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="49">
+        <v>46106</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" s="48">
+        <v>1</v>
+      </c>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="P23" s="30"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:18">
+      <c r="A24" s="11">
+        <v>57021</v>
+      </c>
+      <c r="B24" s="11">
         <v>57015</v>
       </c>
-      <c r="B21" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C21" s="11">
+      <c r="C24" s="11">
         <v>15</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="D24" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G24" s="11">
         <v>1</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H24" s="1">
         <v>9999</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="M21" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="N21" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O21" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="P21" s="40"/>
-    </row>
-    <row r="22" s="10" customFormat="1" spans="1:18">
-      <c r="A22" s="10">
-        <v>57016</v>
-      </c>
-      <c r="B22" s="10">
-        <v>57016</v>
-      </c>
-      <c r="C22" s="10">
-        <v>16</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="O24" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:18">
+      <c r="A25" s="48">
+        <v>57022</v>
+      </c>
+      <c r="B25" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C25" s="1">
+        <v>21</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E25" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="37">
-        <v>46103</v>
-      </c>
-      <c r="G22" s="10">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1">
+        <v>2</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="42" t="s">
         <v>90</v>
-      </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="37"/>
-    </row>
-    <row r="23" s="12" customFormat="1" spans="1:18">
-      <c r="A23" s="12">
-        <v>57017</v>
-      </c>
-      <c r="B23" s="12">
-        <v>57017</v>
-      </c>
-      <c r="C23" s="12">
-        <v>17</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="12">
-        <v>3</v>
-      </c>
-      <c r="I23" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="J23" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K23" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="12">
-        <v>1</v>
-      </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="41"/>
-    </row>
-    <row r="24" s="13" customFormat="1" spans="1:18">
-      <c r="A24" s="12">
-        <v>57018</v>
-      </c>
-      <c r="B24" s="12">
-        <v>57018</v>
-      </c>
-      <c r="C24" s="12">
-        <v>18</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="41"/>
-      <c r="G24" s="12">
-        <v>3</v>
-      </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="J24" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K24" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12">
-        <v>1</v>
-      </c>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-    </row>
-    <row r="25" s="14" customFormat="1" spans="1:18">
-      <c r="A25" s="12">
-        <v>57019</v>
-      </c>
-      <c r="B25" s="14">
-        <v>57019</v>
-      </c>
-      <c r="C25" s="12">
-        <v>19</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="45">
-        <v>46106</v>
-      </c>
-      <c r="G25" s="14">
-        <v>2</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="42" t="s">
-        <v>91</v>
       </c>
       <c r="J25" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12">
+      <c r="K25" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="P25" s="47"/>
-    </row>
-    <row r="26" s="9" customFormat="1" spans="1:18">
-      <c r="A26" s="48">
-        <v>57020</v>
-      </c>
-      <c r="B26" s="9">
-        <v>57020</v>
-      </c>
-      <c r="C26" s="48">
-        <v>20</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="49">
-        <v>46106</v>
-      </c>
-      <c r="G26" s="9">
-        <v>1</v>
-      </c>
-      <c r="H26" s="9">
-        <v>9999</v>
-      </c>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" s="48">
-        <v>1</v>
-      </c>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
-      <c r="P26" s="30"/>
-    </row>
-    <row r="27" s="11" customFormat="1" spans="1:18">
-      <c r="A27" s="11">
-        <v>57021</v>
-      </c>
-      <c r="B27" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C27" s="11">
-        <v>15</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="11">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="M27" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="N27" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="O27" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="P27" s="40"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:18">
-      <c r="A28" s="48">
-        <v>57022</v>
-      </c>
-      <c r="B28" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C28" s="1">
-        <v>21</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1">
-        <v>2</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K28" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
+  <conditionalFormatting sqref="F21">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F22">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
+  <conditionalFormatting sqref="F23">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3648,10 +3274,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3659,7 +3285,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3667,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3675,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3683,7 +3309,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3691,7 +3317,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3699,7 +3325,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3707,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3715,7 +3341,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3723,7 +3349,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3731,7 +3357,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3739,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3747,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3755,7 +3381,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3763,7 +3389,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3771,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3779,7 +3405,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3787,7 +3413,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3795,7 +3421,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -919,12 +919,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="L29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+用户每轮活动的持续时间，单位为小时</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="121">
   <si>
     <t>序列ID</t>
   </si>
@@ -1224,6 +1246,12 @@
   </si>
   <si>
     <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
+  </si>
+  <si>
+    <t>免费旋转活动</t>
+  </si>
+  <si>
+    <t>2026/04/24 00:00:00</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -2498,7 +2526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -3590,6 +3618,38 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="48">
+        <v>57023</v>
+      </c>
+      <c r="B29" s="9">
+        <v>57022</v>
+      </c>
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3648,10 +3708,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3659,7 +3719,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3667,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3675,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3683,7 +3743,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3691,7 +3751,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3699,7 +3759,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3707,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3715,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3723,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3731,7 +3791,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3739,7 +3799,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3747,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3755,7 +3815,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3763,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3771,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3779,7 +3839,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3795,7 +3855,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -937,7 +937,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-用户每轮活动的持续时间，单位为小时</t>
+freespin配置表的轮盘ID</t>
         </r>
       </text>
     </comment>
@@ -946,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="122">
   <si>
     <t>序列ID</t>
   </si>
@@ -1251,7 +1251,10 @@
     <t>免费旋转活动</t>
   </si>
   <si>
-    <t>2026/04/24 00:00:00</t>
+    <t>2026/04/23 00:00:00</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -3644,11 +3647,11 @@
       <c r="J29" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K29" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>72</v>
+      <c r="K29" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3708,10 +3711,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3719,7 +3722,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3727,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3735,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3743,7 +3746,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3751,7 +3754,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3759,7 +3762,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3767,7 +3770,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3775,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3783,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3791,7 +3794,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3799,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3815,7 +3818,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3823,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3831,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3839,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3855,7 +3858,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,225 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0">
+    <comment ref="I13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+秒 分 时 日期1,日期2,日期3 * ？
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+官方派奖：奖池金币数量
+总量 ÷ 平均中奖金额 = 中奖次数
+1000000000 ÷ 718000 = 1392.7577
+========================================
+参数：奖池金币数量_每次消耗积分_转盘类型(从上往下)_资源类型(1 每天开、2定时开)
+统计类型：充值 
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -503,7 +721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0">
+    <comment ref="L16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -522,94 +740,6 @@
           </rPr>
           <t xml:space="preserve">
 对应配置表DailyRewards的ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-获得道具数量_购买原价_实际购买价格</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-渠道ID_商品ID|……</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-期数</t>
         </r>
       </text>
     </comment>
@@ -631,6 +761,72 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+获得道具数量_购买原价_实际购买价格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+渠道ID_商品ID|……</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 期数</t>
         </r>
       </text>
@@ -653,11 +849,33 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-配置表-GrowthFund.xlsx中的ID</t>
+期数</t>
         </r>
       </text>
     </comment>
-    <comment ref="N24" authorId="0">
+    <comment ref="L27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置表-GrowthFund.xlsx中的ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -679,7 +897,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O24" authorId="0">
+    <comment ref="O27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -698,6 +916,28 @@
           </rPr>
           <t xml:space="preserve">
 渠道ID_商品ID|……</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+freespin配置表的轮盘ID</t>
         </r>
       </text>
     </comment>
@@ -706,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="122">
   <si>
     <t>序列ID</t>
   </si>
@@ -906,6 +1146,30 @@
     <t>180000000_10_3_2</t>
   </si>
   <si>
+    <t>59 59 23 9 * ?</t>
+  </si>
+  <si>
+    <t>60000000_10_1_2</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-17号开</t>
+  </si>
+  <si>
+    <t>0 0 0 17 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 19 * ?</t>
+  </si>
+  <si>
+    <t>付费-官方派奖(常驻)-27号开</t>
+  </si>
+  <si>
+    <t>0 0 0 27 * ?</t>
+  </si>
+  <si>
+    <t>59 59 23 29 * ?</t>
+  </si>
+  <si>
     <t>活跃-每日签到(常驻)</t>
   </si>
   <si>
@@ -982,6 +1246,15 @@
   </si>
   <si>
     <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
+  </si>
+  <si>
+    <t>免费旋转活动</t>
+  </si>
+  <si>
+    <t>2026/04/23 00:00:00</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1859,12 +2132,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2256,7 +2529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2643,17 +2916,17 @@
       <c r="J10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="9" t="b">
-        <v>1</v>
+      <c r="K10" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="31" t="s">
+      <c r="M10" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="31"/>
-      <c r="O10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="30"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
@@ -2684,17 +2957,17 @@
       <c r="J11" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="9" t="b">
-        <v>1</v>
+      <c r="K11" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="31" t="s">
+      <c r="M11" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="31"/>
-      <c r="O11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
       <c r="P11" s="30"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
@@ -2725,263 +2998,274 @@
       <c r="J12" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="9" t="b">
-        <v>1</v>
+      <c r="K12" s="31" t="b">
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N12" s="31"/>
-      <c r="O12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="30"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
-        <v>57010</v>
+        <v>57104</v>
       </c>
       <c r="B13" s="9">
-        <v>57010</v>
+        <v>57009</v>
       </c>
       <c r="C13" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G13" s="9">
+        <v>3</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
-        <v>1</v>
-      </c>
-      <c r="H13" s="9">
-        <v>9999</v>
-      </c>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13" s="26"/>
+        <v>54</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>67</v>
+      </c>
       <c r="N13" s="26"/>
       <c r="O13" s="29"/>
       <c r="P13" s="30"/>
     </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="1">
-        <v>57011</v>
-      </c>
-      <c r="B14" s="1">
-        <v>57011</v>
-      </c>
-      <c r="C14" s="1">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
+    <row r="14" s="9" customFormat="1" spans="1:16">
+      <c r="A14" s="9">
+        <v>57105</v>
+      </c>
+      <c r="B14" s="9">
+        <v>57009</v>
+      </c>
+      <c r="C14" s="9">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G14" s="9">
+        <v>3</v>
+      </c>
+      <c r="I14" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9999</v>
+      <c r="J14" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="K14" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+    </row>
+    <row r="15" s="9" customFormat="1" spans="1:16">
+      <c r="A15" s="9">
+        <v>57106</v>
+      </c>
+      <c r="B15" s="9">
+        <v>57009</v>
+      </c>
+      <c r="C15" s="9">
+        <v>9</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="30">
+        <v>46105</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="27"/>
-    </row>
-    <row r="15" s="10" customFormat="1" spans="1:16">
-      <c r="A15" s="10">
+      <c r="L15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M15" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="26"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
+    </row>
+    <row r="16" s="9" customFormat="1" spans="1:16">
+      <c r="A16" s="9">
+        <v>57010</v>
+      </c>
+      <c r="B16" s="9">
+        <v>57010</v>
+      </c>
+      <c r="C16" s="9">
+        <v>10</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="1">
+        <v>57011</v>
+      </c>
+      <c r="B17" s="1">
+        <v>57011</v>
+      </c>
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="K17" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="27"/>
+    </row>
+    <row r="18" s="10" customFormat="1" spans="1:18">
+      <c r="A18" s="10">
         <v>57012</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B18" s="10">
         <v>57012</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C18" s="10">
         <v>12</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G18" s="10">
         <v>1</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H18" s="10">
         <v>9999</v>
       </c>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="34" t="b">
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="37"/>
-    </row>
-    <row r="16" s="10" customFormat="1" spans="1:16">
-      <c r="A16" s="10">
-        <v>57013</v>
-      </c>
-      <c r="B16" s="10">
-        <v>57013</v>
-      </c>
-      <c r="C16" s="10">
-        <v>13</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="37">
-        <v>46101</v>
-      </c>
-      <c r="G16" s="10">
-        <v>2</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="K16" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="37"/>
-    </row>
-    <row r="17" s="10" customFormat="1" spans="1:18">
-      <c r="A17" s="10">
-        <v>57014</v>
-      </c>
-      <c r="B17" s="10">
-        <v>57014</v>
-      </c>
-      <c r="C17" s="10">
-        <v>14</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="37">
-        <v>46102</v>
-      </c>
-      <c r="G17" s="10">
-        <v>2</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="K17" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" s="11" customFormat="1" spans="1:18">
-      <c r="A18" s="11">
-        <v>57015</v>
-      </c>
-      <c r="B18" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C18" s="11">
-        <v>15</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="11">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="N18" s="39" t="s">
+      <c r="L18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="O18" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="P18" s="40"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="37"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
-        <v>57016</v>
+        <v>57013</v>
       </c>
       <c r="B19" s="10">
-        <v>57016</v>
+        <v>57013</v>
       </c>
       <c r="C19" s="10">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="37">
-        <v>46103</v>
+        <v>46101</v>
       </c>
       <c r="G19" s="10">
-        <v>1</v>
-      </c>
-      <c r="H19" s="10">
-        <v>90</v>
-      </c>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="34" t="b">
+        <v>2</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="31" t="b">
         <v>0</v>
       </c>
       <c r="M19" s="35"/>
@@ -2989,273 +3273,426 @@
       <c r="O19" s="36"/>
       <c r="P19" s="37"/>
     </row>
-    <row r="20" s="12" customFormat="1" spans="1:18">
-      <c r="A20" s="12">
+    <row r="20" s="10" customFormat="1" spans="1:18">
+      <c r="A20" s="10">
+        <v>57014</v>
+      </c>
+      <c r="B20" s="10">
+        <v>57014</v>
+      </c>
+      <c r="C20" s="10">
+        <v>14</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="37">
+        <v>46102</v>
+      </c>
+      <c r="G20" s="10">
+        <v>2</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K20" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="37"/>
+    </row>
+    <row r="21" s="11" customFormat="1" spans="1:18">
+      <c r="A21" s="11">
+        <v>57015</v>
+      </c>
+      <c r="B21" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C21" s="11">
+        <v>15</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="N21" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="40"/>
+    </row>
+    <row r="22" s="10" customFormat="1" spans="1:18">
+      <c r="A22" s="10">
+        <v>57016</v>
+      </c>
+      <c r="B22" s="10">
+        <v>57016</v>
+      </c>
+      <c r="C22" s="10">
+        <v>16</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="37">
+        <v>46103</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10">
+        <v>90</v>
+      </c>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="37"/>
+    </row>
+    <row r="23" s="12" customFormat="1" spans="1:18">
+      <c r="A23" s="12">
         <v>57017</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B23" s="12">
         <v>57017</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C23" s="12">
         <v>17</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="12" t="s">
+      <c r="D23" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="12">
+      <c r="F23" s="41"/>
+      <c r="G23" s="12">
         <v>3</v>
       </c>
-      <c r="I20" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="42" t="s">
+      <c r="I23" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="34" t="b">
+      <c r="K23" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L23" s="12">
         <v>1</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="41"/>
-    </row>
-    <row r="21" s="13" customFormat="1" spans="1:18">
-      <c r="A21" s="12">
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="41"/>
+    </row>
+    <row r="24" s="13" customFormat="1" spans="1:18">
+      <c r="A24" s="12">
         <v>57018</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B24" s="12">
         <v>57018</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C24" s="12">
         <v>18</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="12" t="s">
+      <c r="D24" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="12">
+      <c r="F24" s="41"/>
+      <c r="G24" s="12">
         <v>3</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J21" s="42" t="s">
+      <c r="H24" s="12"/>
+      <c r="I24" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="34" t="b">
+      <c r="K24" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L24" s="12">
         <v>1</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-    </row>
-    <row r="22" s="14" customFormat="1" spans="1:18">
-      <c r="A22" s="12">
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="44"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+    </row>
+    <row r="25" s="14" customFormat="1" spans="1:18">
+      <c r="A25" s="12">
         <v>57019</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B25" s="14">
         <v>57019</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C25" s="12">
         <v>19</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="12" t="s">
+      <c r="D25" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F25" s="45">
         <v>46106</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G25" s="14">
         <v>2</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12">
-        <v>1</v>
-      </c>
-      <c r="M22" s="26"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="P22" s="47"/>
-    </row>
-    <row r="23" s="9" customFormat="1" spans="1:18">
-      <c r="A23" s="48">
-        <v>57020</v>
-      </c>
-      <c r="B23" s="9">
-        <v>57020</v>
-      </c>
-      <c r="C23" s="48">
-        <v>20</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="49">
-        <v>46106</v>
-      </c>
-      <c r="G23" s="9">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9">
-        <v>9999</v>
-      </c>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L23" s="48">
-        <v>1</v>
-      </c>
-      <c r="M23" s="26"/>
-      <c r="N23" s="26"/>
-      <c r="P23" s="30"/>
-    </row>
-    <row r="24" s="11" customFormat="1" spans="1:18">
-      <c r="A24" s="11">
-        <v>57021</v>
-      </c>
-      <c r="B24" s="11">
-        <v>57015</v>
-      </c>
-      <c r="C24" s="11">
-        <v>15</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="11">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>9999</v>
-      </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="M24" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="O24" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="P24" s="40"/>
-    </row>
-    <row r="25" customFormat="1" spans="1:18">
-      <c r="A25" s="48">
-        <v>57022</v>
-      </c>
-      <c r="B25" s="9">
-        <v>57021</v>
-      </c>
-      <c r="C25" s="1">
-        <v>21</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1">
-        <v>2</v>
-      </c>
-      <c r="H25" s="1"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J25" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="K25" s="9" t="b">
+      <c r="K25" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12">
         <v>1</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="P25" s="47"/>
+    </row>
+    <row r="26" s="9" customFormat="1" spans="1:18">
+      <c r="A26" s="48">
+        <v>57020</v>
+      </c>
+      <c r="B26" s="9">
+        <v>57020</v>
+      </c>
+      <c r="C26" s="48">
+        <v>20</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="49">
+        <v>46106</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9">
+        <v>9999</v>
+      </c>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" s="48">
+        <v>1</v>
+      </c>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="P26" s="30"/>
+    </row>
+    <row r="27" s="11" customFormat="1" spans="1:18">
+      <c r="A27" s="11">
+        <v>57021</v>
+      </c>
+      <c r="B27" s="11">
+        <v>57015</v>
+      </c>
+      <c r="C27" s="11">
+        <v>15</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="11">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>9999</v>
+      </c>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M27" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="N27" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="O27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="40"/>
+    </row>
+    <row r="28" customFormat="1" spans="1:18">
+      <c r="A28" s="48">
+        <v>57022</v>
+      </c>
+      <c r="B28" s="9">
+        <v>57021</v>
+      </c>
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="48">
+        <v>57023</v>
+      </c>
+      <c r="B29" s="9">
+        <v>57022</v>
+      </c>
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F25">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
+  <conditionalFormatting sqref="F26">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3274,10 +3711,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3285,7 +3722,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3293,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3301,7 +3738,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3309,7 +3746,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3317,7 +3754,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3325,7 +3762,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3333,7 +3770,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3341,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3349,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3357,7 +3794,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3365,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3373,7 +3810,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3381,7 +3818,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3389,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3397,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3405,7 +3842,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3413,7 +3850,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3421,7 +3858,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ActivityConfig" sheetId="1" r:id="rId1"/>
@@ -717,7 +717,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-绑定手机后才可以参加活动</t>
+绑定手机后才可以参加活动
+bindPhone()  绑定手机代码</t>
         </r>
       </text>
     </comment>
@@ -946,7 +947,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t>序列ID</t>
   </si>
@@ -1171,9 +1172,6 @@
   </si>
   <si>
     <t>活跃-每日签到(常驻)</t>
-  </si>
-  <si>
-    <t>bindPhone()</t>
   </si>
   <si>
     <t>1_2_3_4_5_6_7_101_102_103_104_105</t>
@@ -3148,7 +3146,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9">
@@ -3163,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M16" s="26"/>
       <c r="N16" s="26"/>
@@ -3181,7 +3179,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>39</v>
@@ -3213,7 +3211,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>39</v>
@@ -3230,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M18" s="35"/>
       <c r="N18" s="35"/>
@@ -3248,7 +3246,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>39</v>
@@ -3260,10 +3258,10 @@
         <v>2</v>
       </c>
       <c r="I19" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="34" t="s">
         <v>81</v>
-      </c>
-      <c r="J19" s="34" t="s">
-        <v>82</v>
       </c>
       <c r="K19" s="31" t="b">
         <v>0</v>
@@ -3284,7 +3282,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>39</v>
@@ -3296,10 +3294,10 @@
         <v>2</v>
       </c>
       <c r="I20" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="34" t="s">
         <v>81</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>82</v>
       </c>
       <c r="K20" s="31" t="b">
         <v>0</v>
@@ -3320,7 +3318,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>42</v>
@@ -3337,16 +3335,16 @@
         <v>0</v>
       </c>
       <c r="L21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M21" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="M21" s="39" t="s">
+      <c r="N21" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="N21" s="39" t="s">
+      <c r="O21" s="27" t="s">
         <v>87</v>
-      </c>
-      <c r="O21" s="27" t="s">
-        <v>88</v>
       </c>
       <c r="P21" s="40"/>
     </row>
@@ -3361,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
@@ -3396,7 +3394,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>39</v>
@@ -3406,7 +3404,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J23" s="42" t="s">
         <v>44</v>
@@ -3433,7 +3431,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>39</v>
@@ -3444,7 +3442,7 @@
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J24" s="42" t="s">
         <v>44</v>
@@ -3473,7 +3471,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>39</v>
@@ -3486,7 +3484,7 @@
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J25" s="42" t="s">
         <v>44</v>
@@ -3500,7 +3498,7 @@
       <c r="M25" s="26"/>
       <c r="N25" s="26"/>
       <c r="O25" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P25" s="47"/>
     </row>
@@ -3515,7 +3513,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26" s="48" t="s">
         <v>39</v>
@@ -3552,7 +3550,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>42</v>
@@ -3569,16 +3567,16 @@
         <v>1</v>
       </c>
       <c r="L27" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="M27" s="39" t="s">
+      <c r="N27" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="N27" s="39" t="s">
+      <c r="O27" s="27" t="s">
         <v>87</v>
-      </c>
-      <c r="O27" s="27" t="s">
-        <v>88</v>
       </c>
       <c r="P27" s="40"/>
     </row>
@@ -3593,7 +3591,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28" s="48" t="s">
         <v>39</v>
@@ -3604,7 +3602,7 @@
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J28" s="42" t="s">
         <v>44</v>
@@ -3613,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -3633,7 +3631,7 @@
         <v>22</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E29" s="48" t="s">
         <v>39</v>
@@ -3642,7 +3640,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J29" s="42" t="s">
         <v>44</v>
@@ -3651,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3711,10 +3709,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3722,7 +3720,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3730,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3738,7 +3736,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3746,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3754,7 +3752,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3762,7 +3760,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3770,7 +3768,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3778,7 +3776,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3786,7 +3784,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3794,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3802,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3810,7 +3808,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3818,7 +3816,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3826,7 +3824,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3834,7 +3832,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3842,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3850,7 +3848,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3858,7 +3856,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -744,6 +749,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="M20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+配置 ShopRechargeList 中的ID</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="L21" authorId="0">
       <text>
         <r>
@@ -947,7 +974,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="126">
   <si>
     <t>序列ID</t>
   </si>
@@ -1195,7 +1222,10 @@
     <t>2025/09/30 23:59:59</t>
   </si>
   <si>
-    <t>付费-集合礼包</t>
+    <t>付费-合集礼包</t>
+  </si>
+  <si>
+    <t>1001_1002_1003</t>
   </si>
   <si>
     <t>活跃&amp;付费-成长基金(常驻)</t>
@@ -1253,6 +1283,18 @@
   </si>
   <si>
     <t>1_2_3_4_5_6_7_8</t>
+  </si>
+  <si>
+    <t>广告活动</t>
+  </si>
+  <si>
+    <t>2025/01/31 00:00:00</t>
+  </si>
+  <si>
+    <t>2025/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>1001_1002_1003_1004_1005_1006</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1361,9 +1403,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.15"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.15"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1372,12 +1421,6 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFBFBFBF"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1535,7 +1578,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1551,12 +1594,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.0999786370433668"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1912,7 +1949,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1936,16 +1973,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1954,89 +1991,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2064,121 +2101,82 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2527,7 +2525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -2538,7 +2536,7 @@
     <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.25" style="15" customWidth="1"/>
+    <col min="9" max="10" width="21.25" style="14" customWidth="1"/>
     <col min="11" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
@@ -2551,200 +2549,204 @@
   </cols>
   <sheetData>
     <row r="1" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="O2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16" t="s">
+      <c r="D3" s="15"/>
+      <c r="E3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="O3" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="19"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="1">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="18"/>
+    </row>
+    <row r="5" s="9" customFormat="1" spans="1:16">
+      <c r="A5" s="9">
         <v>57002</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="9">
         <v>57002</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="9">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="9"/>
+      <c r="G5" s="9">
         <v>1</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="9">
         <v>9999</v>
       </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
       <c r="K5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="27"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27"/>
     </row>
     <row r="6" s="9" customFormat="1" spans="1:16">
       <c r="A6" s="9">
@@ -2767,10 +2769,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="25" t="s">
         <v>44</v>
       </c>
       <c r="K6" s="9" t="b">
@@ -2779,42 +2781,46 @@
       <c r="L6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="30"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="1">
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27"/>
+    </row>
+    <row r="7" s="9" customFormat="1" spans="1:16">
+      <c r="A7" s="9">
         <v>57004</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="9">
         <v>57004</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="9">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9">
         <v>1</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="9">
         <v>9999</v>
       </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
       <c r="K7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="27"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="27"/>
     </row>
     <row r="8" s="9" customFormat="1" spans="1:16">
       <c r="A8" s="9">
@@ -2839,52 +2845,52 @@
       <c r="H8" s="9">
         <v>9999</v>
       </c>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
       <c r="K8" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="30"/>
-    </row>
-    <row r="9" s="9" customFormat="1" spans="1:16">
-      <c r="A9" s="9">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="27"/>
+    </row>
+    <row r="9" s="10" customFormat="1" spans="1:16">
+      <c r="A9" s="10">
         <v>57006</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>57006</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>6</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9">
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>9999</v>
       </c>
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
-      <c r="K9" s="9" t="b">
+      <c r="K9" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
       <c r="O9" s="29"/>
       <c r="P9" s="30"/>
     </row>
@@ -2904,14 +2910,14 @@
       <c r="E10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="30"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="25" t="s">
         <v>53</v>
       </c>
       <c r="K10" s="31" t="b">
@@ -2925,7 +2931,7 @@
       </c>
       <c r="N10" s="32"/>
       <c r="O10" s="33"/>
-      <c r="P10" s="30"/>
+      <c r="P10" s="27"/>
     </row>
     <row r="11" s="9" customFormat="1" spans="1:16">
       <c r="A11" s="9">
@@ -2943,16 +2949,16 @@
       <c r="E11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="27">
         <v>46105</v>
       </c>
       <c r="G11" s="9">
         <v>3</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="25" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="31" t="b">
@@ -2966,7 +2972,7 @@
       </c>
       <c r="N11" s="32"/>
       <c r="O11" s="33"/>
-      <c r="P11" s="30"/>
+      <c r="P11" s="27"/>
     </row>
     <row r="12" s="9" customFormat="1" spans="1:16">
       <c r="A12" s="9">
@@ -2984,16 +2990,16 @@
       <c r="E12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="27">
         <v>46105</v>
       </c>
       <c r="G12" s="9">
         <v>3</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="25" t="s">
         <v>63</v>
       </c>
       <c r="K12" s="31" t="b">
@@ -3007,7 +3013,7 @@
       </c>
       <c r="N12" s="32"/>
       <c r="O12" s="33"/>
-      <c r="P12" s="30"/>
+      <c r="P12" s="27"/>
     </row>
     <row r="13" s="9" customFormat="1" spans="1:16">
       <c r="A13" s="9">
@@ -3025,16 +3031,16 @@
       <c r="E13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="27">
         <v>46105</v>
       </c>
       <c r="G13" s="9">
         <v>3</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="28" t="s">
+      <c r="J13" s="25" t="s">
         <v>66</v>
       </c>
       <c r="K13" s="9" t="b">
@@ -3046,9 +3052,9 @@
       <c r="M13" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="26"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="30"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27"/>
     </row>
     <row r="14" s="9" customFormat="1" spans="1:16">
       <c r="A14" s="9">
@@ -3066,16 +3072,16 @@
       <c r="E14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="27">
         <v>46105</v>
       </c>
       <c r="G14" s="9">
         <v>3</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="28" t="s">
+      <c r="J14" s="25" t="s">
         <v>70</v>
       </c>
       <c r="K14" s="9" t="b">
@@ -3087,9 +3093,9 @@
       <c r="M14" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="N14" s="26"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="30"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="27"/>
     </row>
     <row r="15" s="9" customFormat="1" spans="1:16">
       <c r="A15" s="9">
@@ -3107,16 +3113,16 @@
       <c r="E15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="27">
         <v>46105</v>
       </c>
       <c r="G15" s="9">
         <v>3</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="25" t="s">
         <v>73</v>
       </c>
       <c r="K15" s="9" t="b">
@@ -3128,9 +3134,9 @@
       <c r="M15" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="30"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27"/>
     </row>
     <row r="16" s="9" customFormat="1" spans="1:16">
       <c r="A16" s="9">
@@ -3155,85 +3161,89 @@
       <c r="H16" s="9">
         <v>9999</v>
       </c>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="30"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="1">
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27"/>
+    </row>
+    <row r="17" s="9" customFormat="1" spans="1:18">
+      <c r="A17" s="9">
         <v>57011</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="9">
         <v>57011</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="9">
         <v>11</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="1">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9">
         <v>1</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="9">
         <v>9999</v>
       </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
       <c r="K17" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L17" s="1">
+      <c r="L17" s="9">
         <v>1</v>
       </c>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="27"/>
-    </row>
-    <row r="18" s="10" customFormat="1" spans="1:18">
-      <c r="A18" s="10">
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27"/>
+    </row>
+    <row r="18" s="9" customFormat="1" spans="1:18">
+      <c r="A18" s="9">
         <v>57012</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>57012</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <v>12</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>1</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>9999</v>
       </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
       <c r="K18" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="37"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="27"/>
     </row>
     <row r="19" s="10" customFormat="1" spans="1:18">
       <c r="A19" s="10">
@@ -3251,102 +3261,103 @@
       <c r="E19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="30">
         <v>46101</v>
       </c>
       <c r="G19" s="10">
         <v>2</v>
       </c>
-      <c r="I19" s="34" t="s">
+      <c r="I19" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="J19" s="34" t="s">
+      <c r="J19" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="K19" s="31" t="b">
+      <c r="K19" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="37"/>
-    </row>
-    <row r="20" s="10" customFormat="1" spans="1:18">
-      <c r="A20" s="10">
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
+    </row>
+    <row r="20" s="9" customFormat="1" spans="1:18">
+      <c r="A20" s="9">
         <v>57014</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>57014</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>14</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="37">
-        <v>46102</v>
-      </c>
-      <c r="G20" s="10">
+      <c r="F20" s="27"/>
+      <c r="G20" s="9">
         <v>2</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="25" t="s">
         <v>81</v>
       </c>
       <c r="K20" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="37"/>
-    </row>
-    <row r="21" s="11" customFormat="1" spans="1:18">
-      <c r="A21" s="11">
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" s="9">
+        <v>1003</v>
+      </c>
+      <c r="N20" s="9"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="27"/>
+    </row>
+    <row r="21" s="9" customFormat="1" spans="1:18">
+      <c r="A21" s="9">
         <v>57015</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>57015</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="9">
         <v>15</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="D21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="9">
         <v>1</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="9">
         <v>9999</v>
       </c>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
       <c r="K21" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="L21" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="M21" s="39" t="s">
+      <c r="L21" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="N21" s="39" t="s">
+      <c r="M21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="O21" s="27" t="s">
+      <c r="N21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="P21" s="40"/>
+      <c r="O21" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="27"/>
     </row>
     <row r="22" s="10" customFormat="1" spans="1:18">
       <c r="A22" s="10">
@@ -3359,12 +3370,12 @@
         <v>16</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="30">
         <v>46103</v>
       </c>
       <c r="G22" s="10">
@@ -3373,284 +3384,346 @@
       <c r="H22" s="10">
         <v>90</v>
       </c>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="31" t="b">
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="37"/>
-    </row>
-    <row r="23" s="12" customFormat="1" spans="1:18">
-      <c r="A23" s="12">
+      <c r="O22" s="29"/>
+      <c r="P22" s="30"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:18">
+      <c r="A23" s="11">
         <v>57017</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>57017</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>17</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="12" t="s">
+      <c r="D23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="12">
+      <c r="F23" s="34"/>
+      <c r="G23" s="11">
         <v>3</v>
       </c>
-      <c r="I23" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J23" s="42" t="s">
+      <c r="I23" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K23" s="31" t="b">
+      <c r="K23" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="11">
         <v>1</v>
       </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="41"/>
-    </row>
-    <row r="24" s="13" customFormat="1" spans="1:18">
-      <c r="A24" s="12">
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="34"/>
+    </row>
+    <row r="24" s="12" customFormat="1" spans="1:18">
+      <c r="A24" s="11">
         <v>57018</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>57018</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <v>18</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" s="34"/>
+      <c r="G24" s="11">
+        <v>3</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="J24" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="11">
+        <v>1</v>
+      </c>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+    </row>
+    <row r="25" s="10" customFormat="1" spans="1:18">
+      <c r="A25" s="11">
+        <v>57019</v>
+      </c>
+      <c r="B25" s="10">
+        <v>57019</v>
+      </c>
+      <c r="C25" s="11">
+        <v>19</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="41"/>
-      <c r="G24" s="12">
-        <v>3</v>
-      </c>
-      <c r="H24" s="12"/>
-      <c r="I24" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J24" s="42" t="s">
+      <c r="F25" s="30">
+        <v>46106</v>
+      </c>
+      <c r="G25" s="10">
+        <v>2</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="J25" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K24" s="31" t="b">
+      <c r="K25" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L25" s="11">
         <v>1</v>
       </c>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="12"/>
-      <c r="R24" s="12"/>
-    </row>
-    <row r="25" s="14" customFormat="1" spans="1:18">
-      <c r="A25" s="12">
-        <v>57019</v>
-      </c>
-      <c r="B25" s="14">
-        <v>57019</v>
-      </c>
-      <c r="C25" s="12">
-        <v>19</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="12" t="s">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="P25" s="30"/>
+    </row>
+    <row r="26" s="10" customFormat="1" spans="1:18">
+      <c r="A26" s="11">
+        <v>57020</v>
+      </c>
+      <c r="B26" s="10">
+        <v>57020</v>
+      </c>
+      <c r="C26" s="11">
+        <v>20</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="45">
+      <c r="F26" s="30">
         <v>46106</v>
       </c>
-      <c r="G25" s="14">
-        <v>2</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="J25" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="K25" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12">
+      <c r="G26" s="10">
         <v>1</v>
       </c>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="P25" s="47"/>
-    </row>
-    <row r="26" s="9" customFormat="1" spans="1:18">
-      <c r="A26" s="48">
-        <v>57020</v>
-      </c>
-      <c r="B26" s="9">
-        <v>57020</v>
-      </c>
-      <c r="C26" s="48">
-        <v>20</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="49">
-        <v>46106</v>
-      </c>
-      <c r="G26" s="9">
-        <v>1</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <v>9999</v>
       </c>
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
-      <c r="K26" s="9" t="b">
+      <c r="K26" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L26" s="48">
+      <c r="L26" s="11">
         <v>1</v>
       </c>
-      <c r="M26" s="26"/>
-      <c r="N26" s="26"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
       <c r="P26" s="30"/>
     </row>
-    <row r="27" s="11" customFormat="1" spans="1:18">
-      <c r="A27" s="11">
+    <row r="27" s="10" customFormat="1" spans="1:18">
+      <c r="A27" s="10">
         <v>57021</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>57015</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>15</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" s="11" t="s">
+      <c r="D27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="10">
         <v>1</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="10">
         <v>9999</v>
       </c>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="9" t="b">
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L27" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="M27" s="39" t="s">
+      <c r="L27" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="N27" s="39" t="s">
+      <c r="M27" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="O27" s="27" t="s">
+      <c r="N27" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="40"/>
-    </row>
-    <row r="28" customFormat="1" spans="1:18">
-      <c r="A28" s="48">
+      <c r="O27" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="30"/>
+    </row>
+    <row r="28" s="13" customFormat="1" spans="1:18">
+      <c r="A28" s="11">
         <v>57022</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>57021</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="10">
         <v>21</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="48" t="s">
+      <c r="D28" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1">
+      <c r="F28" s="10"/>
+      <c r="G28" s="10">
         <v>2</v>
       </c>
-      <c r="H28" s="1"/>
-      <c r="I28" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="J28" s="42" t="s">
+      <c r="H28" s="10"/>
+      <c r="I28" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="J28" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K28" s="9" t="b">
+      <c r="K28" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-    </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="48">
+      <c r="L28" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+    </row>
+    <row r="29" s="10" customFormat="1" spans="1:18">
+      <c r="A29" s="11">
         <v>57023</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>57022</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="10">
         <v>22</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="48" t="s">
+      <c r="D29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="1">
+      <c r="F29" s="10"/>
+      <c r="G29" s="10">
         <v>2</v>
       </c>
-      <c r="I29" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="J29" s="42" t="s">
+      <c r="H29" s="10"/>
+      <c r="I29" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="K29" s="9" t="b">
+      <c r="K29" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="L29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="30"/>
+    </row>
+    <row r="30" s="9" customFormat="1" spans="1:18">
+      <c r="A30" s="9">
+        <v>57025</v>
+      </c>
+      <c r="B30" s="9">
+        <v>57025</v>
+      </c>
+      <c r="C30" s="9">
+        <v>25</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9">
+        <v>2</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="K30" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="27"/>
+    </row>
+    <row r="31" s="9" customFormat="1" spans="1:18">
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="27"/>
+    </row>
+    <row r="32" s="9" customFormat="1" spans="1:18">
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="27"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3709,10 +3782,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3720,7 +3793,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3728,7 +3801,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3736,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3744,7 +3817,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3752,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3760,7 +3833,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3768,7 +3841,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3776,7 +3849,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3784,7 +3857,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3792,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3800,7 +3873,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3808,7 +3881,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3816,7 +3889,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3824,7 +3897,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3832,7 +3905,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3840,7 +3913,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3848,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3856,7 +3929,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -974,7 +974,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="125">
   <si>
     <t>序列ID</t>
   </si>
@@ -1289,9 +1289,6 @@
   </si>
   <si>
     <t>2025/01/31 00:00:00</t>
-  </si>
-  <si>
-    <t>2025/12/31 23:59:59</t>
   </si>
   <si>
     <t>1001_1002_1003_1004_1005_1006</t>
@@ -3303,10 +3300,10 @@
         <v>80</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20" s="31" t="b">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="K20" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="s">
         <v>83</v>
@@ -3692,13 +3689,13 @@
         <v>104</v>
       </c>
       <c r="J30" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="K30" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="K30" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -3782,10 +3779,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3793,7 +3790,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3801,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3809,7 +3806,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3817,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3825,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3833,7 +3830,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3841,7 +3838,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3849,7 +3846,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3857,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3865,7 +3862,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3873,7 +3870,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3881,7 +3878,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3889,7 +3886,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3897,7 +3894,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3905,7 +3902,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3913,7 +3910,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3929,7 +3926,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -811,7 +811,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-获得道具数量_购买原价_实际购买价格</t>
+获得道具数量_购买原价</t>
         </r>
       </text>
     </comment>
@@ -878,6 +878,28 @@
           </rPr>
           <t xml:space="preserve">
 期数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+购买时间_领奖间隔时间    (秒)</t>
         </r>
       </text>
     </comment>
@@ -974,7 +996,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
   <si>
     <t>序列ID</t>
   </si>
@@ -1042,9 +1064,6 @@
     <t>list&lt;BigDecimal&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -1237,34 +1256,40 @@
     <t>1022501_50_1022502_10</t>
   </si>
   <si>
+    <t>37078000_1249.5</t>
+  </si>
+  <si>
+    <t>活跃-收集拼图</t>
+  </si>
+  <si>
+    <t>付费-无尽优惠(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>2025/12/03 00:00:00</t>
+  </si>
+  <si>
+    <t>付费-新游冲刺(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>活动-买一送七(常驻)-时段开</t>
+  </si>
+  <si>
+    <t>2026/01/01 00:00:00</t>
+  </si>
+  <si>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008</t>
+  </si>
+  <si>
+    <t>86400_18000</t>
+  </si>
+  <si>
+    <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)2</t>
+  </si>
+  <si>
     <t>37078000_1249.5_24.99</t>
-  </si>
-  <si>
-    <t>1_google2499|2_ios2499</t>
-  </si>
-  <si>
-    <t>活跃-收集拼图</t>
-  </si>
-  <si>
-    <t>付费-无尽优惠(常驻)-时段开</t>
-  </si>
-  <si>
-    <t>2025/12/03 00:00:00</t>
-  </si>
-  <si>
-    <t>付费-新游冲刺(常驻)-时段开</t>
-  </si>
-  <si>
-    <t>活动-买一送七(常驻)-时段开</t>
-  </si>
-  <si>
-    <t>1_google199|2_ios199</t>
-  </si>
-  <si>
-    <t>活动-财富轮盘-常驻</t>
-  </si>
-  <si>
-    <t>活跃&amp;付费-成长基金(常驻)2</t>
   </si>
   <si>
     <t>活动-充值活动：福利（常驻）时段开</t>
@@ -2538,7 +2563,7 @@
     <col min="12" max="12" width="19.5" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="23.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.825" style="1" customWidth="1"/>
     <col min="16" max="16" width="41.875" style="5" customWidth="1"/>
     <col min="17" max="17" width="9" style="1"/>
     <col min="18" max="18" width="26.75" style="1" customWidth="1"/>
@@ -2637,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="O2" s="21" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="P2" s="18" t="s">
         <v>16</v>
@@ -2645,50 +2670,50 @@
     </row>
     <row r="3" s="8" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="C3" s="15" t="s">
         <v>24</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>25</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="I3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="K3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="L3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="M3" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="N3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="O3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="P3" s="18" t="s">
         <v>36</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" s="8" customFormat="1" ht="15" spans="1:16">
@@ -2720,10 +2745,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9">
@@ -2738,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
@@ -2756,10 +2781,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9">
@@ -2767,16 +2792,16 @@
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="25" t="s">
         <v>43</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>44</v>
       </c>
       <c r="K6" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
@@ -2794,10 +2819,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9">
@@ -2812,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
@@ -2830,10 +2855,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="9">
@@ -2848,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
@@ -2866,10 +2891,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10">
@@ -2884,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
@@ -2902,29 +2927,29 @@
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="9">
         <v>3</v>
       </c>
       <c r="I10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="25" t="s">
         <v>52</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>53</v>
       </c>
       <c r="K10" s="31" t="b">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="32" t="s">
         <v>54</v>
-      </c>
-      <c r="M10" s="32" t="s">
-        <v>55</v>
       </c>
       <c r="N10" s="32"/>
       <c r="O10" s="33"/>
@@ -2941,10 +2966,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="27">
         <v>46105</v>
@@ -2953,19 +2978,19 @@
         <v>3</v>
       </c>
       <c r="I11" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="25" t="s">
         <v>57</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>58</v>
       </c>
       <c r="K11" s="31" t="b">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="32" t="s">
         <v>59</v>
-      </c>
-      <c r="M11" s="32" t="s">
-        <v>60</v>
       </c>
       <c r="N11" s="32"/>
       <c r="O11" s="33"/>
@@ -2982,10 +3007,10 @@
         <v>9</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="27">
         <v>46105</v>
@@ -2994,19 +3019,19 @@
         <v>3</v>
       </c>
       <c r="I12" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="25" t="s">
         <v>62</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>63</v>
       </c>
       <c r="K12" s="31" t="b">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="32" t="s">
         <v>64</v>
-      </c>
-      <c r="M12" s="32" t="s">
-        <v>65</v>
       </c>
       <c r="N12" s="32"/>
       <c r="O12" s="33"/>
@@ -3023,10 +3048,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="27">
         <v>46105</v>
@@ -3035,19 +3060,19 @@
         <v>3</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M13" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="26"/>
@@ -3064,10 +3089,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" s="27">
         <v>46105</v>
@@ -3076,19 +3101,19 @@
         <v>3</v>
       </c>
       <c r="I14" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="25" t="s">
         <v>69</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>70</v>
       </c>
       <c r="K14" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="32" t="s">
         <v>59</v>
-      </c>
-      <c r="M14" s="32" t="s">
-        <v>60</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="26"/>
@@ -3105,10 +3130,10 @@
         <v>9</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" s="27">
         <v>46105</v>
@@ -3117,19 +3142,19 @@
         <v>3</v>
       </c>
       <c r="I15" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="25" t="s">
         <v>72</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>73</v>
       </c>
       <c r="K15" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="32" t="s">
         <v>64</v>
-      </c>
-      <c r="M15" s="32" t="s">
-        <v>65</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="26"/>
@@ -3146,10 +3171,10 @@
         <v>10</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9">
@@ -3164,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
@@ -3182,10 +3207,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9">
@@ -3218,10 +3243,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -3235,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
@@ -3253,10 +3278,10 @@
         <v>13</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="30">
         <v>46101</v>
@@ -3265,10 +3290,10 @@
         <v>2</v>
       </c>
       <c r="I19" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="K19" s="11" t="b">
         <v>0</v>
@@ -3287,26 +3312,26 @@
         <v>14</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="9">
         <v>2</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K20" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M20" s="9">
         <v>1003</v>
@@ -3326,10 +3351,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -3343,16 +3368,16 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="M21" s="9" t="s">
+      <c r="N21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="N21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="O21" s="26" t="s">
-        <v>88</v>
+      <c r="O21" s="26">
+        <v>1001</v>
       </c>
       <c r="P21" s="27"/>
     </row>
@@ -3367,10 +3392,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="30">
         <v>46103</v>
@@ -3400,20 +3425,20 @@
         <v>17</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" s="34"/>
       <c r="G23" s="11">
         <v>3</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K23" s="11" t="b">
         <v>0</v>
@@ -3437,10 +3462,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F24" s="34"/>
       <c r="G24" s="11">
@@ -3448,10 +3473,10 @@
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K24" s="11" t="b">
         <v>0</v>
@@ -3466,47 +3491,49 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" s="10" customFormat="1" spans="1:18">
-      <c r="A25" s="11">
+    <row r="25" s="9" customFormat="1" spans="1:18">
+      <c r="A25" s="31">
         <v>57019</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>57019</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="31">
         <v>19</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="27">
+        <v>46106</v>
+      </c>
+      <c r="G25" s="9">
+        <v>2</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="J25" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="30">
-        <v>46106</v>
-      </c>
-      <c r="G25" s="10">
-        <v>2</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="K25" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="11">
-        <v>1</v>
-      </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="29" t="s">
+      <c r="M25" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="P25" s="30"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="26">
+        <v>1004</v>
+      </c>
+      <c r="P25" s="27"/>
     </row>
     <row r="26" s="10" customFormat="1" spans="1:18">
       <c r="A26" s="11">
@@ -3522,7 +3549,7 @@
         <v>95</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" s="30">
         <v>46106</v>
@@ -3559,7 +3586,7 @@
         <v>96</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" s="10">
         <v>1</v>
@@ -3573,16 +3600,16 @@
         <v>1</v>
       </c>
       <c r="L27" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M27" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="M27" s="10" t="s">
-        <v>86</v>
-      </c>
       <c r="N27" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="O27" s="29" t="s">
-        <v>88</v>
+        <v>97</v>
+      </c>
+      <c r="O27" s="29">
+        <v>1005</v>
       </c>
       <c r="P27" s="30"/>
     </row>
@@ -3597,10 +3624,10 @@
         <v>21</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10">
@@ -3608,16 +3635,16 @@
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K28" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -3637,10 +3664,10 @@
         <v>22</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10">
@@ -3648,16 +3675,16 @@
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -3675,10 +3702,10 @@
         <v>25</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9">
@@ -3686,16 +3713,16 @@
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K30" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -3779,10 +3806,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3790,7 +3817,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3798,7 +3825,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3806,7 +3833,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3814,7 +3841,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3822,7 +3849,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3830,7 +3857,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3838,7 +3865,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3846,7 +3873,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3854,7 +3881,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3862,7 +3889,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3870,7 +3897,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3878,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3886,7 +3913,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3894,7 +3921,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3902,7 +3929,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3910,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3918,7 +3945,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3926,7 +3953,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -996,7 +996,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="127">
   <si>
     <t>序列ID</t>
   </si>
@@ -1274,7 +1274,10 @@
     <t>活动-买一送七(常驻)-时段开</t>
   </si>
   <si>
-    <t>2026/01/01 00:00:00</t>
+    <t>2026/09/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2026/09/07 23:59:59</t>
   </si>
   <si>
     <t>1001_1002_1003_1004_1005_1006_1007_1008</t>
@@ -3518,16 +3521,16 @@
         <v>92</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="K25" s="9" t="b">
         <v>1</v>
       </c>
       <c r="L25" s="31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="26">
@@ -3546,7 +3549,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>38</v>
@@ -3583,7 +3586,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>41</v>
@@ -3606,7 +3609,7 @@
         <v>85</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="29">
         <v>1005</v>
@@ -3624,7 +3627,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>38</v>
@@ -3635,7 +3638,7 @@
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" s="28" t="s">
         <v>43</v>
@@ -3644,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
@@ -3664,7 +3667,7 @@
         <v>22</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>38</v>
@@ -3675,7 +3678,7 @@
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J29" s="28" t="s">
         <v>43</v>
@@ -3684,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10"/>
@@ -3702,7 +3705,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" s="31" t="s">
         <v>38</v>
@@ -3713,7 +3716,7 @@
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J30" s="25" t="s">
         <v>43</v>
@@ -3722,7 +3725,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -3806,10 +3809,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3817,7 +3820,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3825,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3833,7 +3836,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3841,7 +3844,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3849,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3857,7 +3860,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3865,7 +3868,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3873,7 +3876,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3881,7 +3884,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3889,7 +3892,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3897,7 +3900,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3913,7 +3916,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3921,7 +3924,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3929,7 +3932,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3937,7 +3940,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3953,7 +3956,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -991,12 +991,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="M31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+购买时间_领奖间隔时间    (秒)</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="130">
   <si>
     <t>序列ID</t>
   </si>
@@ -1277,49 +1299,58 @@
     <t>2026/09/01 00:00:00</t>
   </si>
   <si>
+    <t>2026/09/06 23:59:59</t>
+  </si>
+  <si>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008</t>
+  </si>
+  <si>
+    <t>66600_120</t>
+  </si>
+  <si>
+    <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)2</t>
+  </si>
+  <si>
+    <t>37078000_1249.5_24.99</t>
+  </si>
+  <si>
+    <t>活动-充值活动：福利（常驻）时段开</t>
+  </si>
+  <si>
+    <t>2026/03/17 00:00:00</t>
+  </si>
+  <si>
+    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
+  </si>
+  <si>
+    <t>免费旋转活动</t>
+  </si>
+  <si>
+    <t>2026/04/23 00:00:00</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
+  </si>
+  <si>
+    <t>广告活动</t>
+  </si>
+  <si>
+    <t>2025/01/31 00:00:00</t>
+  </si>
+  <si>
+    <t>1001_1002_1003_1004_1005_1006</t>
+  </si>
+  <si>
+    <t>2026/09/01 18:30:00</t>
+  </si>
+  <si>
     <t>2026/09/07 23:59:59</t>
   </si>
   <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008</t>
-  </si>
-  <si>
-    <t>86400_18000</t>
-  </si>
-  <si>
-    <t>活动-财富轮盘-常驻</t>
-  </si>
-  <si>
-    <t>活跃&amp;付费-成长基金(常驻)2</t>
-  </si>
-  <si>
-    <t>37078000_1249.5_24.99</t>
-  </si>
-  <si>
-    <t>活动-充值活动：福利（常驻）时段开</t>
-  </si>
-  <si>
-    <t>2026/03/17 00:00:00</t>
-  </si>
-  <si>
-    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
-  </si>
-  <si>
-    <t>免费旋转活动</t>
-  </si>
-  <si>
-    <t>2026/04/23 00:00:00</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8</t>
-  </si>
-  <si>
-    <t>广告活动</t>
-  </si>
-  <si>
-    <t>2025/01/31 00:00:00</t>
-  </si>
-  <si>
-    <t>1001_1002_1003_1004_1005_1006</t>
+    <t>600_120</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1592,12 +1623,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3523,8 +3554,8 @@
       <c r="J25" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="K25" s="9" t="b">
-        <v>1</v>
+      <c r="K25" s="11" t="b">
+        <v>0</v>
       </c>
       <c r="L25" s="31" t="s">
         <v>94</v>
@@ -3733,13 +3764,46 @@
       <c r="P30" s="27"/>
     </row>
     <row r="31" s="9" customFormat="1" spans="1:18">
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
+      <c r="A31" s="31">
+        <v>57033</v>
+      </c>
+      <c r="B31" s="9">
+        <v>57019</v>
+      </c>
+      <c r="C31" s="31">
+        <v>19</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="27">
+        <v>46106</v>
+      </c>
+      <c r="G31" s="9">
+        <v>2</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
+      <c r="O31" s="26">
+        <v>1004</v>
+      </c>
       <c r="P31" s="27"/>
     </row>
     <row r="32" s="9" customFormat="1" spans="1:18">
@@ -3754,43 +3818,46 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
+  <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
+  <conditionalFormatting sqref="F24">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
+  <conditionalFormatting sqref="F25">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
+  <conditionalFormatting sqref="F26">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="F31">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3809,10 +3876,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3820,7 +3887,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3828,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3836,7 +3903,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3844,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3852,7 +3919,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3860,7 +3927,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3868,7 +3935,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3876,7 +3943,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3884,7 +3951,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3892,7 +3959,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3900,7 +3967,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3908,7 +3975,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3916,7 +3983,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3924,7 +3991,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3932,7 +3999,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -3940,7 +4007,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -3956,7 +4023,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">

--- a/table/resources/sample/ActivityConfig.xlsx
+++ b/table/resources/sample/ActivityConfig.xlsx
@@ -881,29 +881,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M25" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-购买时间_领奖间隔时间    (秒)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L27" authorId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -925,7 +903,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N27" authorId="0">
+    <comment ref="N26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -947,7 +925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O27" authorId="0">
+    <comment ref="O26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -969,7 +947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L29" authorId="0">
+    <comment ref="L28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -991,7 +969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0">
+    <comment ref="M30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1018,7 +996,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="127">
   <si>
     <t>序列ID</t>
   </si>
@@ -1293,64 +1271,55 @@
     <t>付费-新游冲刺(常驻)-时段开</t>
   </si>
   <si>
+    <t>活动-财富轮盘-常驻</t>
+  </si>
+  <si>
+    <t>活跃&amp;付费-成长基金(常驻)2</t>
+  </si>
+  <si>
+    <t>37078000_1249.5_24.99</t>
+  </si>
+  <si>
+    <t>活动-充值活动：福利（常驻）时段开</t>
+  </si>
+  <si>
+    <t>2026/03/17 00:00:00</t>
+  </si>
+  <si>
+    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
+  </si>
+  <si>
+    <t>免费旋转活动</t>
+  </si>
+  <si>
+    <t>2026/04/23 00:00:00</t>
+  </si>
+  <si>
+    <t>1_2_3_4_5_6_7_8</t>
+  </si>
+  <si>
+    <t>广告活动</t>
+  </si>
+  <si>
+    <t>2025/01/31 00:00:00</t>
+  </si>
+  <si>
+    <t>1001_1002_1003_1004_1005_1006</t>
+  </si>
+  <si>
     <t>活动-买一送七(常驻)-时段开</t>
   </si>
   <si>
-    <t>2026/09/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/09/06 23:59:59</t>
+    <t>2026/09/10 00:00:00</t>
+  </si>
+  <si>
+    <t>2026/09/16 23:59:59</t>
   </si>
   <si>
     <t>1001_1002_1003_1004_1005_1006_1007_1008</t>
   </si>
   <si>
-    <t>66600_120</t>
-  </si>
-  <si>
-    <t>活动-财富轮盘-常驻</t>
-  </si>
-  <si>
-    <t>活跃&amp;付费-成长基金(常驻)2</t>
-  </si>
-  <si>
-    <t>37078000_1249.5_24.99</t>
-  </si>
-  <si>
-    <t>活动-充值活动：福利（常驻）时段开</t>
-  </si>
-  <si>
-    <t>2026/03/17 00:00:00</t>
-  </si>
-  <si>
-    <t>1_1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1015_1016_1017_1018_1019_2001_2002_2003</t>
-  </si>
-  <si>
-    <t>免费旋转活动</t>
-  </si>
-  <si>
-    <t>2026/04/23 00:00:00</t>
-  </si>
-  <si>
-    <t>1_2_3_4_5_6_7_8</t>
-  </si>
-  <si>
-    <t>广告活动</t>
-  </si>
-  <si>
-    <t>2025/01/31 00:00:00</t>
-  </si>
-  <si>
-    <t>1001_1002_1003_1004_1005_1006</t>
-  </si>
-  <si>
-    <t>2026/09/01 18:30:00</t>
-  </si>
-  <si>
-    <t>2026/09/07 23:59:59</t>
-  </si>
-  <si>
-    <t>600_120</t>
+    <t>259200_18000</t>
   </si>
   <si>
     <t>#备注1</t>
@@ -1623,12 +1592,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2581,7 +2550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
@@ -3525,68 +3494,58 @@
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
     </row>
-    <row r="25" s="9" customFormat="1" spans="1:18">
-      <c r="A25" s="31">
-        <v>57019</v>
-      </c>
-      <c r="B25" s="9">
-        <v>57019</v>
-      </c>
-      <c r="C25" s="31">
-        <v>19</v>
-      </c>
-      <c r="D25" s="31" t="s">
+    <row r="25" s="10" customFormat="1" spans="1:18">
+      <c r="A25" s="11">
+        <v>57020</v>
+      </c>
+      <c r="B25" s="10">
+        <v>57020</v>
+      </c>
+      <c r="C25" s="11">
+        <v>20</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="30">
         <v>46106</v>
       </c>
-      <c r="G25" s="9">
-        <v>2</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="25" t="s">
+      <c r="G25" s="10">
+        <v>1</v>
+      </c>
+      <c r="H25" s="10">
+        <v>9999</v>
+      </c>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" s="11">
+        <v>1</v>
+      </c>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="P25" s="30"/>
+    </row>
+    <row r="26" s="10" customFormat="1" spans="1:18">
+      <c r="A26" s="10">
+        <v>57021</v>
+      </c>
+      <c r="B26" s="10">
+        <v>57015</v>
+      </c>
+      <c r="C26" s="10">
+        <v>15</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="J25" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="K25" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="26">
-        <v>1004</v>
-      </c>
-      <c r="P25" s="27"/>
-    </row>
-    <row r="26" s="10" customFormat="1" spans="1:18">
-      <c r="A26" s="11">
-        <v>57020</v>
-      </c>
-      <c r="B26" s="10">
-        <v>57020</v>
-      </c>
-      <c r="C26" s="11">
-        <v>20</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="30">
-        <v>46106</v>
+      <c r="E26" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -3599,66 +3558,72 @@
       <c r="K26" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="L26" s="11">
-        <v>1</v>
-      </c>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
+      <c r="L26" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O26" s="29">
+        <v>1005</v>
+      </c>
       <c r="P26" s="30"/>
     </row>
-    <row r="27" s="10" customFormat="1" spans="1:18">
-      <c r="A27" s="10">
+    <row r="27" s="13" customFormat="1" spans="1:18">
+      <c r="A27" s="11">
+        <v>57022</v>
+      </c>
+      <c r="B27" s="10">
         <v>57021</v>
       </c>
-      <c r="B27" s="10">
-        <v>57015</v>
-      </c>
       <c r="C27" s="10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>41</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="10"/>
       <c r="G27" s="10">
-        <v>1</v>
-      </c>
-      <c r="H27" s="10">
-        <v>9999</v>
-      </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+        <v>2</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>43</v>
+      </c>
       <c r="K27" s="10" t="b">
         <v>1</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="O27" s="29">
-        <v>1005</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
       <c r="P27" s="30"/>
-    </row>
-    <row r="28" s="13" customFormat="1" spans="1:18">
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+    </row>
+    <row r="28" s="10" customFormat="1" spans="1:18">
       <c r="A28" s="11">
+        <v>57023</v>
+      </c>
+      <c r="B28" s="10">
         <v>57022</v>
       </c>
-      <c r="B28" s="10">
-        <v>57021</v>
-      </c>
       <c r="C28" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>38</v>
@@ -3669,7 +3634,7 @@
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J28" s="28" t="s">
         <v>43</v>
@@ -3678,143 +3643,103 @@
         <v>1</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10"/>
       <c r="O28" s="10"/>
       <c r="P28" s="30"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-    </row>
-    <row r="29" s="10" customFormat="1" spans="1:18">
-      <c r="A29" s="11">
-        <v>57023</v>
-      </c>
-      <c r="B29" s="10">
-        <v>57022</v>
-      </c>
-      <c r="C29" s="10">
-        <v>22</v>
-      </c>
-      <c r="D29" s="10" t="s">
+    </row>
+    <row r="29" s="9" customFormat="1" spans="1:18">
+      <c r="A29" s="9">
+        <v>57025</v>
+      </c>
+      <c r="B29" s="9">
+        <v>57025</v>
+      </c>
+      <c r="C29" s="9">
+        <v>25</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9">
+        <v>2</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10">
-        <v>2</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="28" t="s">
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="27"/>
+    </row>
+    <row r="30" s="9" customFormat="1" spans="1:18">
+      <c r="A30" s="31">
+        <v>57050</v>
+      </c>
+      <c r="B30" s="9">
+        <v>57019</v>
+      </c>
+      <c r="C30" s="31">
+        <v>19</v>
+      </c>
+      <c r="D30" s="31" t="s">
         <v>103</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="30"/>
-    </row>
-    <row r="30" s="9" customFormat="1" spans="1:18">
-      <c r="A30" s="9">
-        <v>57025</v>
-      </c>
-      <c r="B30" s="9">
-        <v>57025</v>
-      </c>
-      <c r="C30" s="9">
-        <v>25</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="E30" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="9"/>
+      <c r="F30" s="27">
+        <v>46106</v>
+      </c>
       <c r="G30" s="9">
         <v>2</v>
       </c>
-      <c r="H30" s="9"/>
       <c r="I30" s="25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="K30" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="M30" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+      <c r="O30" s="26">
+        <v>1004</v>
+      </c>
       <c r="P30" s="27"/>
     </row>
     <row r="31" s="9" customFormat="1" spans="1:18">
-      <c r="A31" s="31">
-        <v>57033</v>
-      </c>
-      <c r="B31" s="9">
-        <v>57019</v>
-      </c>
-      <c r="C31" s="31">
-        <v>19</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="27">
-        <v>46106</v>
-      </c>
-      <c r="G31" s="9">
-        <v>2</v>
-      </c>
-      <c r="I31" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="K31" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L31" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>110</v>
-      </c>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
       <c r="N31" s="9"/>
-      <c r="O31" s="26">
-        <v>1004</v>
-      </c>
+      <c r="O31" s="9"/>
       <c r="P31" s="27"/>
-    </row>
-    <row r="32" s="9" customFormat="1" spans="1:18">
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="27"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F10">
@@ -3851,12 +3776,9 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F31">
+  <conditionalFormatting sqref="F30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3876,10 +3798,10 @@
   <sheetData>
     <row r="5" ht="16.5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:2">
@@ -3887,7 +3809,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:2">
@@ -3895,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:2">
@@ -3903,7 +3825,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:2">
@@ -3911,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:2">
@@ -3919,7 +3841,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:2">
@@ -3927,7 +3849,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -3935,7 +3857,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:2">
@@ -3943,7 +3865,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:2">
@@ -3951,7 +3873,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:2">
@@ -3959,7 +3881,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:2">
@@ -3967,7 +3889,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
@@ -3975,7 +3897,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
@@ -3983,7 +3905,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
@@ -3991,7 +3913,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
@@ -3999,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
@@ -4007,7 +3929,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
@@ -4023,7 +3945,7 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" ht="21.95" customHeight="1" spans="1:4">
